--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T15:58:27+00:00</t>
+    <t>2026-01-23T10:30:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-23T10:30:04+00:00</t>
+    <t>2026-01-27T15:50:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-27T15:50:42+00:00</t>
+    <t>2026-01-28T14:07:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3133,34 +3133,34 @@
     <t>Bundle.entry:DUITaskPrestation.response.outcome</t>
   </si>
   <si>
-    <t>Bundle.entry:RelatedPerson</t>
-  </si>
-  <si>
-    <t>RelatedPerson</t>
-  </si>
-  <si>
-    <t>RelatedPerson conforming to the FrCoreRelatedPerson profile, used to convey information about the user's contacts.</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.link</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.fullUrl</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.resource</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RelatedPerson {https://hl7.fr/ig/fhir/core/StructureDefinition/fr-core-related-person|2.1.0}
+    <t>Bundle.entry:DUIRelatedPersonContact</t>
+  </si>
+  <si>
+    <t>DUIRelatedPersonContact</t>
+  </si>
+  <si>
+    <t>RelatedPerson conforming to the TDDUIRelatedPersonContact profile, used to convey information about the contact person.</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.link</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.fullUrl</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.resource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RelatedPerson {https://interop.esante.gouv.fr/ig/fhir/tddui/StructureDefinition/tddui-related-person-contact|2.2.0-ballot}
 </t>
   </si>
   <si>
@@ -3173,79 +3173,79 @@
     <t>role</t>
   </si>
   <si>
-    <t>Bundle.entry:RelatedPerson.search</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.mode</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.search.score</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.method</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.url</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifNoneMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifModifiedSince</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifMatch</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.request.ifNoneExist</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.id</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.extension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.modifierExtension</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.status</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.location</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.etag</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.lastModified</t>
-  </si>
-  <si>
-    <t>Bundle.entry:RelatedPerson.response.outcome</t>
+    <t>Bundle.entry:DUIRelatedPersonContact.search</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.mode</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.search.score</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.method</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.url</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifNoneMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifModifiedSince</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifMatch</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.request.ifNoneExist</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.id</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.extension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.modifierExtension</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.status</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.location</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.etag</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.lastModified</t>
+  </si>
+  <si>
+    <t>Bundle.entry:DUIRelatedPersonContact.response.outcome</t>
   </si>
   <si>
     <t>Bundle.signature</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T14:07:57+00:00</t>
+    <t>2026-01-29T08:29:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-29T08:29:40+00:00</t>
+    <t>2026-01-30T16:24:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-30T16:24:47+00:00</t>
+    <t>2026-02-02T09:56:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-02T09:56:46+00:00</t>
+    <t>2026-02-04T09:47:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T09:47:16+00:00</t>
+    <t>2026-02-04T14:08:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
+++ b/414-rc---contact/ig/StructureDefinition-tddui-bundle.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-04T14:08:59+00:00</t>
+    <t>2026-02-04T16:27:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
